--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1378,32 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307103</v>
+        <v>128307933</v>
       </c>
       <c r="B9" t="n">
-        <v>91806</v>
+        <v>79061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625824</v>
+        <v>625837</v>
       </c>
       <c r="R9" t="n">
-        <v>6900490</v>
+        <v>6900371</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307933</v>
+        <v>128307103</v>
       </c>
       <c r="B10" t="n">
-        <v>79061</v>
+        <v>91806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625837</v>
+        <v>625824</v>
       </c>
       <c r="R10" t="n">
-        <v>6900371</v>
+        <v>6900490</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1378,32 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307933</v>
+        <v>128307103</v>
       </c>
       <c r="B9" t="n">
-        <v>79061</v>
+        <v>91806</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625837</v>
+        <v>625824</v>
       </c>
       <c r="R9" t="n">
-        <v>6900371</v>
+        <v>6900490</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307103</v>
+        <v>128307933</v>
       </c>
       <c r="B10" t="n">
-        <v>91806</v>
+        <v>79061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625824</v>
+        <v>625837</v>
       </c>
       <c r="R10" t="n">
-        <v>6900490</v>
+        <v>6900371</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128307051</v>
+        <v>128310161</v>
       </c>
       <c r="B6" t="n">
-        <v>91648</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,37 +1084,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625813</v>
+        <v>625891</v>
       </c>
       <c r="R6" t="n">
-        <v>6900495</v>
+        <v>6900473</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128310161</v>
+        <v>128307051</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>91648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,51 +1195,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625891</v>
+        <v>625813</v>
       </c>
       <c r="R7" t="n">
-        <v>6900473</v>
+        <v>6900495</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1771,45 +1771,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128308770</v>
+        <v>128306755</v>
       </c>
       <c r="B13" t="n">
-        <v>91317</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lomyran, Lomyran, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625918</v>
+        <v>625719</v>
       </c>
       <c r="R13" t="n">
-        <v>6900458</v>
+        <v>6900559</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1868,50 +1873,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128306755</v>
+        <v>128308770</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>91317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran, Lomyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625719</v>
+        <v>625918</v>
       </c>
       <c r="R14" t="n">
-        <v>6900559</v>
+        <v>6900458</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128310161</v>
+        <v>128307051</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>91648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,51 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625891</v>
+        <v>625813</v>
       </c>
       <c r="R6" t="n">
-        <v>6900473</v>
+        <v>6900495</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128307051</v>
+        <v>128310161</v>
       </c>
       <c r="B7" t="n">
-        <v>91648</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,37 +1181,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625813</v>
+        <v>625891</v>
       </c>
       <c r="R7" t="n">
-        <v>6900495</v>
+        <v>6900473</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1771,50 +1771,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128306755</v>
+        <v>128308770</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>91317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran, Lomyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625719</v>
+        <v>625918</v>
       </c>
       <c r="R13" t="n">
-        <v>6900559</v>
+        <v>6900458</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1873,45 +1868,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128308770</v>
+        <v>128306755</v>
       </c>
       <c r="B14" t="n">
-        <v>91317</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lomyran, Lomyran, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625918</v>
+        <v>625719</v>
       </c>
       <c r="R14" t="n">
-        <v>6900458</v>
+        <v>6900559</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128307051</v>
+        <v>128310161</v>
       </c>
       <c r="B6" t="n">
-        <v>91648</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,37 +1084,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625813</v>
+        <v>625891</v>
       </c>
       <c r="R6" t="n">
-        <v>6900495</v>
+        <v>6900473</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128310161</v>
+        <v>128307051</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>91648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,51 +1195,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625891</v>
+        <v>625813</v>
       </c>
       <c r="R7" t="n">
-        <v>6900473</v>
+        <v>6900495</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128310161</v>
+        <v>128307051</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>91648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,51 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625891</v>
+        <v>625813</v>
       </c>
       <c r="R6" t="n">
-        <v>6900473</v>
+        <v>6900495</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128307051</v>
+        <v>128310161</v>
       </c>
       <c r="B7" t="n">
-        <v>91648</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,37 +1181,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625813</v>
+        <v>625891</v>
       </c>
       <c r="R7" t="n">
-        <v>6900495</v>
+        <v>6900473</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,32 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307103</v>
+        <v>128307933</v>
       </c>
       <c r="B9" t="n">
-        <v>91806</v>
+        <v>79061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625824</v>
+        <v>625837</v>
       </c>
       <c r="R9" t="n">
-        <v>6900490</v>
+        <v>6900371</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307933</v>
+        <v>128307103</v>
       </c>
       <c r="B10" t="n">
-        <v>79061</v>
+        <v>91806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625837</v>
+        <v>625824</v>
       </c>
       <c r="R10" t="n">
-        <v>6900371</v>
+        <v>6900490</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306889</v>
       </c>
       <c r="B2" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128310183</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128310140</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128307894</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128307051</v>
       </c>
       <c r="B6" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128310161</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128308103</v>
       </c>
       <c r="B8" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128307933</v>
       </c>
       <c r="B9" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128307103</v>
       </c>
       <c r="B10" t="n">
-        <v>91806</v>
+        <v>91814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128308265</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128308185</v>
       </c>
       <c r="B12" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128308770</v>
       </c>
       <c r="B13" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128306755</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306889</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128310183</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128310140</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128307894</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128307051</v>
       </c>
       <c r="B6" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128310161</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128308103</v>
       </c>
       <c r="B8" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128307933</v>
       </c>
       <c r="B9" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128307103</v>
       </c>
       <c r="B10" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128308265</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128308185</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128308770</v>
       </c>
       <c r="B13" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128306755</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128307051</v>
+        <v>128310161</v>
       </c>
       <c r="B6" t="n">
-        <v>91748</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,37 +1084,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625813</v>
+        <v>625891</v>
       </c>
       <c r="R6" t="n">
-        <v>6900495</v>
+        <v>6900473</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128310161</v>
+        <v>128307051</v>
       </c>
       <c r="B7" t="n">
-        <v>57682</v>
+        <v>91748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,51 +1195,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625891</v>
+        <v>625813</v>
       </c>
       <c r="R7" t="n">
-        <v>6900473</v>
+        <v>6900495</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,32 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307933</v>
+        <v>128307103</v>
       </c>
       <c r="B9" t="n">
-        <v>79115</v>
+        <v>91906</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625837</v>
+        <v>625824</v>
       </c>
       <c r="R9" t="n">
-        <v>6900371</v>
+        <v>6900490</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307103</v>
+        <v>128307933</v>
       </c>
       <c r="B10" t="n">
-        <v>91906</v>
+        <v>79115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625824</v>
+        <v>625837</v>
       </c>
       <c r="R10" t="n">
-        <v>6900490</v>
+        <v>6900371</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1771,45 +1771,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128308770</v>
+        <v>128306755</v>
       </c>
       <c r="B13" t="n">
-        <v>91417</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lomyran, Lomyran, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625918</v>
+        <v>625719</v>
       </c>
       <c r="R13" t="n">
-        <v>6900458</v>
+        <v>6900559</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1868,50 +1873,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128306755</v>
+        <v>128308770</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>91417</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran, Lomyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625719</v>
+        <v>625918</v>
       </c>
       <c r="R14" t="n">
-        <v>6900559</v>
+        <v>6900458</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128306889</v>
+        <v>128310183</v>
       </c>
       <c r="B2" t="n">
-        <v>91417</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625733</v>
+        <v>625777</v>
       </c>
       <c r="R2" t="n">
-        <v>6900527</v>
+        <v>6900329</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,53 +777,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128310183</v>
+        <v>128306889</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>91417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625777</v>
+        <v>625733</v>
       </c>
       <c r="R3" t="n">
-        <v>6900329</v>
+        <v>6900527</v>
       </c>
       <c r="S3" t="n">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1771,50 +1771,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128306755</v>
+        <v>128308770</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>91417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran, Lomyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625719</v>
+        <v>625918</v>
       </c>
       <c r="R13" t="n">
-        <v>6900559</v>
+        <v>6900458</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1873,45 +1868,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128308770</v>
+        <v>128306755</v>
       </c>
       <c r="B14" t="n">
-        <v>91417</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lomyran, Lomyran, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625918</v>
+        <v>625719</v>
       </c>
       <c r="R14" t="n">
-        <v>6900458</v>
+        <v>6900559</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1378,32 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307103</v>
+        <v>128307933</v>
       </c>
       <c r="B9" t="n">
-        <v>91906</v>
+        <v>79115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625824</v>
+        <v>625837</v>
       </c>
       <c r="R9" t="n">
-        <v>6900490</v>
+        <v>6900371</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307933</v>
+        <v>128307103</v>
       </c>
       <c r="B10" t="n">
-        <v>79115</v>
+        <v>91906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625837</v>
+        <v>625824</v>
       </c>
       <c r="R10" t="n">
-        <v>6900371</v>
+        <v>6900490</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128310183</v>
+        <v>128306889</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>91429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625777</v>
+        <v>625733</v>
       </c>
       <c r="R2" t="n">
-        <v>6900329</v>
+        <v>6900527</v>
       </c>
       <c r="S2" t="n">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,48 +772,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128306889</v>
+        <v>128310183</v>
       </c>
       <c r="B3" t="n">
-        <v>91417</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625733</v>
+        <v>625777</v>
       </c>
       <c r="R3" t="n">
-        <v>6900527</v>
+        <v>6900329</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128310140</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128307894</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128310161</v>
+        <v>128307051</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>91760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,51 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625891</v>
+        <v>625813</v>
       </c>
       <c r="R6" t="n">
-        <v>6900473</v>
+        <v>6900495</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128307051</v>
+        <v>128310161</v>
       </c>
       <c r="B7" t="n">
-        <v>91748</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,37 +1181,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625813</v>
+        <v>625891</v>
       </c>
       <c r="R7" t="n">
-        <v>6900495</v>
+        <v>6900473</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128308103</v>
       </c>
       <c r="B8" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,32 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307933</v>
+        <v>128307103</v>
       </c>
       <c r="B9" t="n">
-        <v>79115</v>
+        <v>91918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625837</v>
+        <v>625824</v>
       </c>
       <c r="R9" t="n">
-        <v>6900371</v>
+        <v>6900490</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307103</v>
+        <v>128307933</v>
       </c>
       <c r="B10" t="n">
-        <v>91906</v>
+        <v>79119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625824</v>
+        <v>625837</v>
       </c>
       <c r="R10" t="n">
-        <v>6900490</v>
+        <v>6900371</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1575,7 +1575,7 @@
         <v>128308265</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128308185</v>
       </c>
       <c r="B12" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,45 +1771,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128308770</v>
+        <v>128306755</v>
       </c>
       <c r="B13" t="n">
-        <v>91417</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lomyran, Lomyran, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625918</v>
+        <v>625719</v>
       </c>
       <c r="R13" t="n">
-        <v>6900458</v>
+        <v>6900559</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1868,50 +1873,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128306755</v>
+        <v>128308770</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>91429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran, Lomyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625719</v>
+        <v>625918</v>
       </c>
       <c r="R14" t="n">
-        <v>6900559</v>
+        <v>6900458</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128306889</v>
+        <v>128310183</v>
       </c>
       <c r="B2" t="n">
-        <v>91429</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625733</v>
+        <v>625777</v>
       </c>
       <c r="R2" t="n">
-        <v>6900527</v>
+        <v>6900329</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,53 +777,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128310183</v>
+        <v>128306889</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>91429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625777</v>
+        <v>625733</v>
       </c>
       <c r="R3" t="n">
-        <v>6900329</v>
+        <v>6900527</v>
       </c>
       <c r="S3" t="n">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128307051</v>
+        <v>128310161</v>
       </c>
       <c r="B6" t="n">
-        <v>91760</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,37 +1084,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625813</v>
+        <v>625891</v>
       </c>
       <c r="R6" t="n">
-        <v>6900495</v>
+        <v>6900473</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1170,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128310161</v>
+        <v>128307051</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>91760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,51 +1195,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625891</v>
+        <v>625813</v>
       </c>
       <c r="R7" t="n">
-        <v>6900473</v>
+        <v>6900495</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,32 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307103</v>
+        <v>128307933</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>79119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625824</v>
+        <v>625837</v>
       </c>
       <c r="R9" t="n">
-        <v>6900490</v>
+        <v>6900371</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307933</v>
+        <v>128307103</v>
       </c>
       <c r="B10" t="n">
-        <v>79119</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625837</v>
+        <v>625824</v>
       </c>
       <c r="R10" t="n">
-        <v>6900371</v>
+        <v>6900490</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1771,50 +1771,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128306755</v>
+        <v>128308770</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>91429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran, Lomyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625719</v>
+        <v>625918</v>
       </c>
       <c r="R13" t="n">
-        <v>6900559</v>
+        <v>6900458</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1873,45 +1868,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128308770</v>
+        <v>128306755</v>
       </c>
       <c r="B14" t="n">
-        <v>91429</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lomyran, Lomyran, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625918</v>
+        <v>625719</v>
       </c>
       <c r="R14" t="n">
-        <v>6900458</v>
+        <v>6900559</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128310183</v>
+        <v>128306889</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>91431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625777</v>
+        <v>625733</v>
       </c>
       <c r="R2" t="n">
-        <v>6900329</v>
+        <v>6900527</v>
       </c>
       <c r="S2" t="n">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,48 +772,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128306889</v>
+        <v>128310183</v>
       </c>
       <c r="B3" t="n">
-        <v>91429</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625733</v>
+        <v>625777</v>
       </c>
       <c r="R3" t="n">
-        <v>6900527</v>
+        <v>6900329</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128307894</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128310161</v>
+        <v>128307051</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>91762</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,51 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625891</v>
+        <v>625813</v>
       </c>
       <c r="R6" t="n">
-        <v>6900473</v>
+        <v>6900495</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128307051</v>
+        <v>128310161</v>
       </c>
       <c r="B7" t="n">
-        <v>91760</v>
+        <v>57686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,37 +1181,51 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625813</v>
+        <v>625891</v>
       </c>
       <c r="R7" t="n">
-        <v>6900495</v>
+        <v>6900473</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128308103</v>
       </c>
       <c r="B8" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128307933</v>
       </c>
       <c r="B9" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128307103</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128308185</v>
       </c>
       <c r="B12" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128308770</v>
       </c>
       <c r="B13" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306889</v>
       </c>
       <c r="B2" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128307051</v>
       </c>
       <c r="B6" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128308103</v>
       </c>
       <c r="B8" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128307103</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128308185</v>
       </c>
       <c r="B12" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128308770</v>
       </c>
       <c r="B13" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1378,32 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307933</v>
+        <v>128307103</v>
       </c>
       <c r="B9" t="n">
-        <v>79121</v>
+        <v>91921</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625837</v>
+        <v>625824</v>
       </c>
       <c r="R9" t="n">
-        <v>6900371</v>
+        <v>6900490</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307103</v>
+        <v>128307933</v>
       </c>
       <c r="B10" t="n">
-        <v>91921</v>
+        <v>79121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625824</v>
+        <v>625837</v>
       </c>
       <c r="R10" t="n">
-        <v>6900490</v>
+        <v>6900371</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306889</v>
       </c>
       <c r="B2" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128310183</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128310140</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128307894</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128307051</v>
       </c>
       <c r="B6" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128310161</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128308103</v>
       </c>
       <c r="B8" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>128307103</v>
       </c>
       <c r="B9" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>128307933</v>
       </c>
       <c r="B10" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128308265</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128308185</v>
       </c>
       <c r="B12" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>128308770</v>
       </c>
       <c r="B13" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128306755</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -1378,32 +1378,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307103</v>
+        <v>128307933</v>
       </c>
       <c r="B9" t="n">
-        <v>91948</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625824</v>
+        <v>625837</v>
       </c>
       <c r="R9" t="n">
-        <v>6900490</v>
+        <v>6900371</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1475,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307933</v>
+        <v>128307103</v>
       </c>
       <c r="B10" t="n">
-        <v>79148</v>
+        <v>91948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625837</v>
+        <v>625824</v>
       </c>
       <c r="R10" t="n">
-        <v>6900371</v>
+        <v>6900490</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>128310140</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128308265</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128306755</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -877,7 +877,7 @@
         <v>128310140</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>128308265</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>128306755</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128306889</v>
+        <v>128307933</v>
       </c>
       <c r="B2" t="n">
-        <v>91469</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625733</v>
+        <v>625837</v>
       </c>
       <c r="R2" t="n">
-        <v>6900527</v>
+        <v>6900371</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128310183</v>
+        <v>128307051</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625777</v>
+        <v>625813</v>
       </c>
       <c r="R3" t="n">
-        <v>6900329</v>
+        <v>6900495</v>
       </c>
       <c r="S3" t="n">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128310140</v>
+        <v>128307103</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625756</v>
+        <v>625824</v>
       </c>
       <c r="R4" t="n">
-        <v>6900335</v>
+        <v>6900490</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128307894</v>
+        <v>128308103</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625819</v>
+        <v>625856</v>
       </c>
       <c r="R5" t="n">
-        <v>6900356</v>
+        <v>6900358</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128307051</v>
+        <v>128308185</v>
       </c>
       <c r="B6" t="n">
-        <v>91800</v>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625813</v>
+        <v>625866</v>
       </c>
       <c r="R6" t="n">
-        <v>6900495</v>
+        <v>6900367</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,62 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128310161</v>
+        <v>128306889</v>
       </c>
       <c r="B7" t="n">
-        <v>57713</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
+          <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625891</v>
+        <v>625733</v>
       </c>
       <c r="R7" t="n">
-        <v>6900473</v>
+        <v>6900527</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1281,48 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128308103</v>
+        <v>128308770</v>
       </c>
       <c r="B8" t="n">
-        <v>92786</v>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran, Lomyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625856</v>
+        <v>625918</v>
       </c>
       <c r="R8" t="n">
-        <v>6900358</v>
+        <v>6900458</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128307103</v>
+        <v>128307335</v>
       </c>
       <c r="B9" t="n">
-        <v>91958</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,34 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran, Lomyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625824</v>
+        <v>625852</v>
       </c>
       <c r="R9" t="n">
-        <v>6900490</v>
+        <v>6900493</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1475,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128307933</v>
+        <v>128307894</v>
       </c>
       <c r="B10" t="n">
-        <v>79152</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625837</v>
+        <v>625819</v>
       </c>
       <c r="R10" t="n">
-        <v>6900371</v>
+        <v>6900356</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1572,27 +1548,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128308265</v>
+        <v>128310161</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1600,10 +1576,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1612,13 +1597,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625912</v>
+        <v>625891</v>
       </c>
       <c r="R11" t="n">
-        <v>6900474</v>
+        <v>6900473</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128308185</v>
+        <v>128306755</v>
       </c>
       <c r="B12" t="n">
-        <v>92786</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1685,34 +1670,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trossmyran, Trossmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625866</v>
+        <v>625719</v>
       </c>
       <c r="R12" t="n">
-        <v>6900367</v>
+        <v>6900559</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1771,45 +1761,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128308770</v>
+        <v>128307364</v>
       </c>
       <c r="B13" t="n">
-        <v>91469</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lomyran, Lomyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625918</v>
+        <v>625851</v>
       </c>
       <c r="R13" t="n">
-        <v>6900458</v>
+        <v>6900499</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1842,6 +1837,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tydliga ringhack på tall, svårt att avgöra ålder på hacken</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1868,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128306755</v>
+        <v>128308265</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1904,14 +1904,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Trossmyran, Trossmyran, Mpd</t>
+          <t>Lomyran,  Njurunda, Lomyran,  Njurunda, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625719</v>
+        <v>625912</v>
       </c>
       <c r="R14" t="n">
-        <v>6900559</v>
+        <v>6900474</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1967,6 +1967,324 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128310140</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Trossmyran, Trossmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>625756</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6900335</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128922608</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Trossmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>625686</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6900481</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128307460</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Trossmyran, Trossmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>625836</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6900501</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36953-2025 artfynd.xlsx
+++ b/artfynd/A 36953-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307933</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307051</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307103</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128308103</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128308185</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128306889</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128308770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307335</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307894</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1656,6 +1706,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128310161</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1758,6 +1813,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128306755</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307364</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1967,6 +2032,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128308265</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2069,6 +2139,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128310140</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2188,6 +2263,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128922608</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2285,8 +2365,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128307460</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>